--- a/backend/data/financials_by_company/0ICU.L.xlsx
+++ b/backend/data/financials_by_company/0ICU.L.xlsx
@@ -677,610 +677,610 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>10237448.401123</v>
+        <v>18082532.083927</v>
       </c>
       <c r="C2" t="n">
-        <v>0.268699</v>
+        <v>0.266704</v>
       </c>
       <c r="D2" t="n">
-        <v>2124000000</v>
+        <v>2207200000</v>
       </c>
       <c r="E2" t="n">
-        <v>38100000</v>
+        <v>67800000</v>
       </c>
       <c r="F2" t="n">
-        <v>38100000</v>
+        <v>67800000</v>
       </c>
       <c r="G2" t="n">
-        <v>1328700000</v>
+        <v>1439900000</v>
       </c>
       <c r="H2" t="n">
-        <v>270400000</v>
+        <v>252500000</v>
       </c>
       <c r="I2" t="n">
-        <v>4429900000</v>
+        <v>3388200000</v>
       </c>
       <c r="J2" t="n">
-        <v>2162100000</v>
+        <v>2275000000</v>
       </c>
       <c r="K2" t="n">
-        <v>1891700000</v>
+        <v>2022500000</v>
       </c>
       <c r="L2" t="n">
-        <v>166300000</v>
+        <v>79000000</v>
       </c>
       <c r="M2" t="n">
-        <v>74800000</v>
+        <v>58900000</v>
       </c>
       <c r="N2" t="n">
-        <v>155700000</v>
+        <v>113500000</v>
       </c>
       <c r="O2" t="n">
-        <v>1300837448.401123</v>
+        <v>1390182532.083927</v>
       </c>
       <c r="P2" t="n">
-        <v>1328700000</v>
+        <v>1439900000</v>
       </c>
       <c r="Q2" t="n">
-        <v>4629200000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>198400000</v>
-      </c>
+        <v>3452200000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>1612500000</v>
+        <v>1816900000</v>
       </c>
       <c r="T2" t="n">
-        <v>86554743</v>
+        <v>86104901</v>
       </c>
       <c r="U2" t="n">
-        <v>86124079</v>
+        <v>85511379</v>
       </c>
       <c r="V2" t="n">
-        <v>15.35</v>
+        <v>16.72</v>
       </c>
       <c r="W2" t="n">
-        <v>15.43</v>
+        <v>16.84</v>
       </c>
       <c r="X2" t="n">
-        <v>1328700000</v>
+        <v>1439900000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1328700000</v>
+        <v>1439900000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1328700000</v>
+        <v>1439900000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1328700000</v>
+        <v>1439900000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1328700000</v>
+        <v>1439900000</v>
       </c>
       <c r="AC2" t="n">
-        <v>488200000</v>
+        <v>523700000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1816900000</v>
+        <v>1963600000</v>
       </c>
       <c r="AE2" t="n">
-        <v>40100000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2000000</v>
-      </c>
+        <v>67800000</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>1800000</v>
+        <v>100000</v>
       </c>
       <c r="AH2" t="n">
-        <v>600000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-1200000</v>
-      </c>
+        <v>100000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>38100000</v>
+        <v>67700000</v>
       </c>
       <c r="AK2" t="n">
-        <v>166300000</v>
+        <v>79000000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-85400000</v>
+        <v>-24400000</v>
       </c>
       <c r="AM2" t="n">
-        <v>74800000</v>
+        <v>58900000</v>
       </c>
       <c r="AN2" t="n">
-        <v>155700000</v>
+        <v>113500000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1610500000</v>
+        <v>1816800000</v>
       </c>
       <c r="AP2" t="n">
-        <v>199300000</v>
+        <v>64000000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6800000</v>
+        <v>-76100000</v>
       </c>
       <c r="AR2" t="n">
-        <v>192500000</v>
+        <v>64000000</v>
       </c>
       <c r="AS2" t="n">
-        <v>192500000</v>
+        <v>64000000</v>
       </c>
       <c r="AT2" t="n">
-        <v>76800000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>115700000</v>
-      </c>
+        <v>64000000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>1809800000</v>
+        <v>1880800000</v>
       </c>
       <c r="AW2" t="n">
-        <v>4429900000</v>
+        <v>3388200000</v>
       </c>
       <c r="AX2" t="n">
-        <v>6239700000</v>
+        <v>5269000000</v>
       </c>
       <c r="AY2" t="n">
-        <v>6239700000</v>
+        <v>5269000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>20965666.508539</v>
+        <v>38930210.547973</v>
       </c>
       <c r="C3" t="n">
-        <v>0.240157</v>
+        <v>0.229271</v>
       </c>
       <c r="D3" t="n">
-        <v>1887000000</v>
+        <v>1628800000</v>
       </c>
       <c r="E3" t="n">
-        <v>87300000</v>
+        <v>169800000</v>
       </c>
       <c r="F3" t="n">
-        <v>87300000</v>
+        <v>169800000</v>
       </c>
       <c r="G3" t="n">
-        <v>1281400000</v>
+        <v>1123800000</v>
       </c>
       <c r="H3" t="n">
-        <v>217500000</v>
+        <v>267600000</v>
       </c>
       <c r="I3" t="n">
-        <v>3911000000</v>
+        <v>3741500000</v>
       </c>
       <c r="J3" t="n">
-        <v>1974300000</v>
+        <v>1798600000</v>
       </c>
       <c r="K3" t="n">
-        <v>1756800000</v>
+        <v>1531000000</v>
       </c>
       <c r="L3" t="n">
-        <v>176300000</v>
+        <v>72500000</v>
       </c>
       <c r="M3" t="n">
-        <v>70400000</v>
+        <v>72900000</v>
       </c>
       <c r="N3" t="n">
-        <v>195900000</v>
+        <v>117600000</v>
       </c>
       <c r="O3" t="n">
-        <v>1215065666.508539</v>
+        <v>992930210.547973</v>
       </c>
       <c r="P3" t="n">
-        <v>1281400000</v>
+        <v>1123800000</v>
       </c>
       <c r="Q3" t="n">
-        <v>4083900000</v>
+        <v>3902700000</v>
       </c>
       <c r="R3" t="n">
-        <v>152300000</v>
+        <v>139000000</v>
       </c>
       <c r="S3" t="n">
-        <v>1422800000</v>
+        <v>1307100000</v>
       </c>
       <c r="T3" t="n">
-        <v>86496220</v>
+        <v>86096413</v>
       </c>
       <c r="U3" t="n">
-        <v>85953885</v>
+        <v>85676080</v>
       </c>
       <c r="V3" t="n">
-        <v>14.82</v>
+        <v>13.06</v>
       </c>
       <c r="W3" t="n">
-        <v>14.91</v>
+        <v>13.12</v>
       </c>
       <c r="X3" t="n">
-        <v>1281400000</v>
+        <v>1123800000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1281400000</v>
+        <v>1123800000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1281400000</v>
+        <v>1123800000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1281400000</v>
+        <v>1123800000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1281400000</v>
+        <v>1123800000</v>
       </c>
       <c r="AC3" t="n">
-        <v>405000000</v>
+        <v>334300000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1686400000</v>
+        <v>1458100000</v>
       </c>
       <c r="AE3" t="n">
-        <v>97700000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>10400000</v>
-      </c>
+        <v>169800000</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>10300000</v>
+        <v>91300000</v>
       </c>
       <c r="AH3" t="n">
-        <v>10300000</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>6600000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-84700000</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>87300000</v>
+        <v>78500000</v>
       </c>
       <c r="AK3" t="n">
-        <v>176300000</v>
+        <v>72500000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-50800000</v>
+        <v>-27800000</v>
       </c>
       <c r="AM3" t="n">
-        <v>70400000</v>
+        <v>72900000</v>
       </c>
       <c r="AN3" t="n">
-        <v>195900000</v>
+        <v>117600000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1412400000</v>
+        <v>1215800000</v>
       </c>
       <c r="AP3" t="n">
-        <v>172900000</v>
+        <v>161200000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4600000</v>
+        <v>15200000</v>
       </c>
       <c r="AR3" t="n">
-        <v>168300000</v>
+        <v>146000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>168300000</v>
+        <v>146000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>67300000</v>
+        <v>127600000</v>
       </c>
       <c r="AU3" t="n">
-        <v>22000000</v>
+        <v>18400000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1585300000</v>
+        <v>1377000000</v>
       </c>
       <c r="AW3" t="n">
-        <v>3911000000</v>
+        <v>3741500000</v>
       </c>
       <c r="AX3" t="n">
-        <v>5496300000</v>
+        <v>5118500000</v>
       </c>
       <c r="AY3" t="n">
-        <v>5496300000</v>
+        <v>5118500000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>38930210.547973</v>
+        <v>20965666.508539</v>
       </c>
       <c r="C4" t="n">
-        <v>0.229271</v>
+        <v>0.240157</v>
       </c>
       <c r="D4" t="n">
-        <v>1628800000</v>
+        <v>1887000000</v>
       </c>
       <c r="E4" t="n">
-        <v>169800000</v>
+        <v>87300000</v>
       </c>
       <c r="F4" t="n">
-        <v>169800000</v>
+        <v>87300000</v>
       </c>
       <c r="G4" t="n">
-        <v>1123800000</v>
+        <v>1281400000</v>
       </c>
       <c r="H4" t="n">
-        <v>267600000</v>
+        <v>217500000</v>
       </c>
       <c r="I4" t="n">
-        <v>3741500000</v>
+        <v>3911000000</v>
       </c>
       <c r="J4" t="n">
-        <v>1798600000</v>
+        <v>1974300000</v>
       </c>
       <c r="K4" t="n">
-        <v>1531000000</v>
+        <v>1756800000</v>
       </c>
       <c r="L4" t="n">
-        <v>72500000</v>
+        <v>176300000</v>
       </c>
       <c r="M4" t="n">
-        <v>72900000</v>
+        <v>70400000</v>
       </c>
       <c r="N4" t="n">
-        <v>117600000</v>
+        <v>195900000</v>
       </c>
       <c r="O4" t="n">
-        <v>992930210.547973</v>
+        <v>1215065666.508539</v>
       </c>
       <c r="P4" t="n">
-        <v>1123800000</v>
+        <v>1281400000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3902700000</v>
+        <v>4083900000</v>
       </c>
       <c r="R4" t="n">
-        <v>139000000</v>
+        <v>152300000</v>
       </c>
       <c r="S4" t="n">
-        <v>1307100000</v>
+        <v>1422800000</v>
       </c>
       <c r="T4" t="n">
-        <v>86096413</v>
+        <v>86496220</v>
       </c>
       <c r="U4" t="n">
-        <v>85676080</v>
+        <v>85953885</v>
       </c>
       <c r="V4" t="n">
-        <v>13.06</v>
+        <v>14.82</v>
       </c>
       <c r="W4" t="n">
-        <v>13.12</v>
+        <v>14.91</v>
       </c>
       <c r="X4" t="n">
-        <v>1123800000</v>
+        <v>1281400000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1123800000</v>
+        <v>1281400000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1123800000</v>
+        <v>1281400000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1123800000</v>
+        <v>1281400000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1123800000</v>
+        <v>1281400000</v>
       </c>
       <c r="AC4" t="n">
-        <v>334300000</v>
+        <v>405000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1458100000</v>
+        <v>1686400000</v>
       </c>
       <c r="AE4" t="n">
-        <v>169800000</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>97700000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>10400000</v>
+      </c>
       <c r="AG4" t="n">
-        <v>91300000</v>
+        <v>10300000</v>
       </c>
       <c r="AH4" t="n">
-        <v>6600000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-84700000</v>
-      </c>
+        <v>10300000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>78500000</v>
+        <v>87300000</v>
       </c>
       <c r="AK4" t="n">
-        <v>72500000</v>
+        <v>176300000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-27800000</v>
+        <v>-50800000</v>
       </c>
       <c r="AM4" t="n">
-        <v>72900000</v>
+        <v>70400000</v>
       </c>
       <c r="AN4" t="n">
-        <v>117600000</v>
+        <v>195900000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1215800000</v>
+        <v>1412400000</v>
       </c>
       <c r="AP4" t="n">
-        <v>161200000</v>
+        <v>172900000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15200000</v>
+        <v>4600000</v>
       </c>
       <c r="AR4" t="n">
-        <v>146000000</v>
+        <v>168300000</v>
       </c>
       <c r="AS4" t="n">
-        <v>146000000</v>
+        <v>168300000</v>
       </c>
       <c r="AT4" t="n">
-        <v>127600000</v>
+        <v>67300000</v>
       </c>
       <c r="AU4" t="n">
-        <v>18400000</v>
+        <v>22000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1377000000</v>
+        <v>1585300000</v>
       </c>
       <c r="AW4" t="n">
-        <v>3741500000</v>
+        <v>3911000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>5118500000</v>
+        <v>5496300000</v>
       </c>
       <c r="AY4" t="n">
-        <v>5118500000</v>
+        <v>5496300000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>18082532.083927</v>
+        <v>10237448.401123</v>
       </c>
       <c r="C5" t="n">
-        <v>0.266704</v>
+        <v>0.268699</v>
       </c>
       <c r="D5" t="n">
-        <v>2207200000</v>
+        <v>2124000000</v>
       </c>
       <c r="E5" t="n">
-        <v>67800000</v>
+        <v>38100000</v>
       </c>
       <c r="F5" t="n">
-        <v>67800000</v>
+        <v>38100000</v>
       </c>
       <c r="G5" t="n">
-        <v>1439900000</v>
+        <v>1328700000</v>
       </c>
       <c r="H5" t="n">
-        <v>252500000</v>
+        <v>270400000</v>
       </c>
       <c r="I5" t="n">
-        <v>3388200000</v>
+        <v>4429900000</v>
       </c>
       <c r="J5" t="n">
-        <v>2275000000</v>
+        <v>2162100000</v>
       </c>
       <c r="K5" t="n">
-        <v>2022500000</v>
+        <v>1891700000</v>
       </c>
       <c r="L5" t="n">
-        <v>79000000</v>
+        <v>166300000</v>
       </c>
       <c r="M5" t="n">
-        <v>58900000</v>
+        <v>74800000</v>
       </c>
       <c r="N5" t="n">
-        <v>113500000</v>
+        <v>155700000</v>
       </c>
       <c r="O5" t="n">
-        <v>1390182532.083927</v>
+        <v>1300837448.401123</v>
       </c>
       <c r="P5" t="n">
-        <v>1439900000</v>
+        <v>1328700000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3452200000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>4629200000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>198400000</v>
+      </c>
       <c r="S5" t="n">
+        <v>1612500000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>86554743</v>
+      </c>
+      <c r="U5" t="n">
+        <v>86124079</v>
+      </c>
+      <c r="V5" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="W5" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1328700000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1328700000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1328700000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1328700000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1328700000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>488200000</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1816900000</v>
       </c>
-      <c r="T5" t="n">
-        <v>86104901</v>
-      </c>
-      <c r="U5" t="n">
-        <v>85511379</v>
-      </c>
-      <c r="V5" t="n">
-        <v>16.72</v>
-      </c>
-      <c r="W5" t="n">
-        <v>16.84</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1439900000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1439900000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1439900000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1439900000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1439900000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>523700000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1963600000</v>
-      </c>
       <c r="AE5" t="n">
-        <v>67800000</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>40100000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2000000</v>
+      </c>
       <c r="AG5" t="n">
-        <v>100000</v>
+        <v>1800000</v>
       </c>
       <c r="AH5" t="n">
-        <v>100000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>600000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1200000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>67700000</v>
+        <v>38100000</v>
       </c>
       <c r="AK5" t="n">
-        <v>79000000</v>
+        <v>166300000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-24400000</v>
+        <v>-85400000</v>
       </c>
       <c r="AM5" t="n">
-        <v>58900000</v>
+        <v>74800000</v>
       </c>
       <c r="AN5" t="n">
-        <v>113500000</v>
+        <v>155700000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1816800000</v>
+        <v>1610500000</v>
       </c>
       <c r="AP5" t="n">
-        <v>64000000</v>
+        <v>199300000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-76100000</v>
+        <v>6800000</v>
       </c>
       <c r="AR5" t="n">
-        <v>64000000</v>
+        <v>192500000</v>
       </c>
       <c r="AS5" t="n">
-        <v>64000000</v>
+        <v>192500000</v>
       </c>
       <c r="AT5" t="n">
-        <v>64000000</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>76800000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>115700000</v>
+      </c>
       <c r="AV5" t="n">
-        <v>1880800000</v>
+        <v>1809800000</v>
       </c>
       <c r="AW5" t="n">
-        <v>3388200000</v>
+        <v>4429900000</v>
       </c>
       <c r="AX5" t="n">
-        <v>5269000000</v>
+        <v>6239700000</v>
       </c>
       <c r="AY5" t="n">
-        <v>5269000000</v>
+        <v>6239700000</v>
       </c>
     </row>
   </sheetData>
@@ -1606,744 +1606,744 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>3090081</v>
+        <v>9474920</v>
       </c>
       <c r="C2" t="n">
-        <v>861498630</v>
+        <v>855113791</v>
       </c>
       <c r="D2" t="n">
         <v>864588711</v>
       </c>
       <c r="E2" t="n">
-        <v>29200000</v>
+        <v>54800000</v>
       </c>
       <c r="F2" t="n">
-        <v>6889400000</v>
+        <v>4820400000</v>
       </c>
       <c r="G2" t="n">
-        <v>6889400000</v>
+        <v>4820400000</v>
       </c>
       <c r="H2" t="n">
-        <v>540100000</v>
+        <v>2141200000</v>
       </c>
       <c r="I2" t="n">
-        <v>6889400000</v>
+        <v>4820400000</v>
       </c>
       <c r="J2" t="n">
-        <v>29200000</v>
+        <v>54800000</v>
       </c>
       <c r="K2" t="n">
-        <v>6889400000</v>
+        <v>4820400000</v>
       </c>
       <c r="L2" t="n">
-        <v>6889400000</v>
+        <v>4820400000</v>
       </c>
       <c r="M2" t="n">
-        <v>6889400000</v>
+        <v>4820400000</v>
       </c>
       <c r="N2" t="n">
-        <v>6889400000</v>
+        <v>4820400000</v>
       </c>
       <c r="O2" t="n">
-        <v>697200000</v>
+        <v>-1337500000</v>
       </c>
       <c r="P2" t="n">
-        <v>6192200000</v>
+        <v>6157900000</v>
       </c>
       <c r="Q2" t="n">
-        <v>6192200000</v>
+        <v>6157900000</v>
       </c>
       <c r="R2" t="n">
-        <v>2561000000</v>
+        <v>1527600000</v>
       </c>
       <c r="S2" t="n">
-        <v>1607500000</v>
+        <v>996100000</v>
       </c>
       <c r="T2" t="n">
-        <v>10400000</v>
+        <v>10300000</v>
       </c>
       <c r="U2" t="n">
-        <v>10400000</v>
+        <v>10300000</v>
       </c>
       <c r="V2" t="n">
-        <v>958000000</v>
+        <v>377100000</v>
       </c>
       <c r="W2" t="n">
-        <v>958000000</v>
+        <v>377100000</v>
       </c>
       <c r="X2" t="n">
-        <v>22300000</v>
+        <v>37900000</v>
       </c>
       <c r="Y2" t="n">
-        <v>22300000</v>
+        <v>37900000</v>
       </c>
       <c r="Z2" t="n">
-        <v>616800000</v>
+        <v>570800000</v>
       </c>
       <c r="AA2" t="n">
-        <v>953500000</v>
+        <v>531500000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6900000</v>
+        <v>16900000</v>
       </c>
       <c r="AC2" t="n">
-        <v>6900000</v>
+        <v>16900000</v>
       </c>
       <c r="AD2" t="n">
-        <v>158900000</v>
+        <v>127400000</v>
       </c>
       <c r="AE2" t="n">
-        <v>787700000</v>
+        <v>387200000</v>
       </c>
       <c r="AF2" t="n">
-        <v>36700000</v>
+        <v>25000000</v>
       </c>
       <c r="AG2" t="n">
-        <v>751000000</v>
+        <v>362200000</v>
       </c>
       <c r="AH2" t="n">
-        <v>30400000</v>
+        <v>9300000</v>
       </c>
       <c r="AI2" t="n">
-        <v>720600000</v>
+        <v>352900000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9450400000</v>
+        <v>6348000000</v>
       </c>
       <c r="AK2" t="n">
-        <v>7956800000</v>
+        <v>3675300000</v>
       </c>
       <c r="AL2" t="n">
-        <v>45600000</v>
+        <v>40500000</v>
       </c>
       <c r="AM2" t="n">
-        <v>23400000</v>
+        <v>5800000</v>
       </c>
       <c r="AN2" t="n">
-        <v>23400000</v>
+        <v>5800000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1092900000</v>
+        <v>819300000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1092900000</v>
+        <v>819300000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6794900000</v>
+        <v>2809700000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-2494500000</v>
+        <v>-2059100000</v>
       </c>
       <c r="AS2" t="n">
-        <v>9289400000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3219600000</v>
-      </c>
+        <v>4868800000</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>1493600000</v>
+        <v>2672700000</v>
       </c>
       <c r="AV2" t="n">
-        <v>12300000</v>
+        <v>10300000</v>
       </c>
       <c r="AW2" t="n">
-        <v>159100000</v>
+        <v>17400000</v>
       </c>
       <c r="AX2" t="n">
-        <v>460000000</v>
+        <v>340000000</v>
       </c>
       <c r="AY2" t="n">
-        <v>105600000</v>
+        <v>49900000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>79900000</v>
+        <v>59600000</v>
       </c>
       <c r="BA2" t="n">
-        <v>274500000</v>
+        <v>230500000</v>
       </c>
       <c r="BB2" t="n">
-        <v>353000000</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
+        <v>135300000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-1200000</v>
+      </c>
       <c r="BD2" t="n">
-        <v>44500000</v>
+        <v>20000000</v>
       </c>
       <c r="BE2" t="n">
-        <v>306400000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>58800000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>56500000</v>
+      </c>
       <c r="BG2" t="n">
-        <v>509200000</v>
+        <v>2169700000</v>
       </c>
       <c r="BH2" t="n">
-        <v>509200000</v>
+        <v>2169700000</v>
       </c>
       <c r="BI2" t="n">
-        <v>392400000</v>
+        <v>2069200000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>116800000</v>
+        <v>100500000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>3896663</v>
+        <v>6612266</v>
       </c>
       <c r="C3" t="n">
-        <v>860692048</v>
+        <v>857976445</v>
       </c>
       <c r="D3" t="n">
         <v>864588711</v>
       </c>
       <c r="E3" t="n">
-        <v>39700000</v>
+        <v>52300000</v>
       </c>
       <c r="F3" t="n">
-        <v>6274100000</v>
+        <v>5439900000</v>
       </c>
       <c r="G3" t="n">
-        <v>6274100000</v>
+        <v>5439900000</v>
       </c>
       <c r="H3" t="n">
-        <v>2495500000</v>
+        <v>2451500000</v>
       </c>
       <c r="I3" t="n">
-        <v>6274100000</v>
+        <v>5439900000</v>
       </c>
       <c r="J3" t="n">
-        <v>39700000</v>
+        <v>52300000</v>
       </c>
       <c r="K3" t="n">
-        <v>6274100000</v>
+        <v>5439900000</v>
       </c>
       <c r="L3" t="n">
-        <v>6274100000</v>
+        <v>5439900000</v>
       </c>
       <c r="M3" t="n">
-        <v>6274100000</v>
+        <v>5439900000</v>
       </c>
       <c r="N3" t="n">
-        <v>6274100000</v>
+        <v>5439900000</v>
       </c>
       <c r="O3" t="n">
-        <v>86200000</v>
+        <v>-733400000</v>
       </c>
       <c r="P3" t="n">
-        <v>6187900000</v>
+        <v>6173300000</v>
       </c>
       <c r="Q3" t="n">
-        <v>6187900000</v>
+        <v>6173300000</v>
       </c>
       <c r="R3" t="n">
-        <v>1880400000</v>
+        <v>1638300000</v>
       </c>
       <c r="S3" t="n">
-        <v>1161700000</v>
+        <v>1012800000</v>
       </c>
       <c r="T3" t="n">
-        <v>10500000</v>
+        <v>10400000</v>
       </c>
       <c r="U3" t="n">
-        <v>10500000</v>
+        <v>10400000</v>
       </c>
       <c r="V3" t="n">
-        <v>560700000</v>
+        <v>451900000</v>
       </c>
       <c r="W3" t="n">
-        <v>560700000</v>
+        <v>451900000</v>
       </c>
       <c r="X3" t="n">
-        <v>28400000</v>
+        <v>32800000</v>
       </c>
       <c r="Y3" t="n">
-        <v>28400000</v>
+        <v>32800000</v>
       </c>
       <c r="Z3" t="n">
-        <v>562100000</v>
+        <v>517700000</v>
       </c>
       <c r="AA3" t="n">
-        <v>718700000</v>
+        <v>625500000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11300000</v>
+        <v>19500000</v>
       </c>
       <c r="AC3" t="n">
-        <v>11300000</v>
+        <v>19500000</v>
       </c>
       <c r="AD3" t="n">
-        <v>146600000</v>
+        <v>143200000</v>
       </c>
       <c r="AE3" t="n">
-        <v>560800000</v>
+        <v>462800000</v>
       </c>
       <c r="AF3" t="n">
-        <v>28500000</v>
+        <v>25900000</v>
       </c>
       <c r="AG3" t="n">
-        <v>532300000</v>
+        <v>436900000</v>
       </c>
       <c r="AH3" t="n">
-        <v>7200000</v>
+        <v>7800000</v>
       </c>
       <c r="AI3" t="n">
-        <v>525100000</v>
+        <v>429100000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8154500000</v>
+        <v>7078200000</v>
       </c>
       <c r="AK3" t="n">
-        <v>4940300000</v>
+        <v>4001200000</v>
       </c>
       <c r="AL3" t="n">
-        <v>39700000</v>
+        <v>40400000</v>
       </c>
       <c r="AM3" t="n">
-        <v>32800000</v>
+        <v>14500000</v>
       </c>
       <c r="AN3" t="n">
-        <v>32800000</v>
+        <v>14500000</v>
       </c>
       <c r="AO3" t="n">
-        <v>958300000</v>
+        <v>862200000</v>
       </c>
       <c r="AP3" t="n">
-        <v>958300000</v>
+        <v>862200000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3909500000</v>
+        <v>3084100000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-2294900000</v>
+        <v>-2083600000</v>
       </c>
       <c r="AS3" t="n">
-        <v>6204400000</v>
+        <v>5167700000</v>
       </c>
       <c r="AT3" t="n">
-        <v>498000000</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3214200000</v>
+        <v>3077000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>11400000</v>
+        <v>10700000</v>
       </c>
       <c r="AW3" t="n">
-        <v>199100000</v>
+        <v>19200000</v>
       </c>
       <c r="AX3" t="n">
-        <v>413600000</v>
+        <v>389300000</v>
       </c>
       <c r="AY3" t="n">
-        <v>82800000</v>
+        <v>64800000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>67900000</v>
+        <v>75100000</v>
       </c>
       <c r="BA3" t="n">
-        <v>262900000</v>
+        <v>249400000</v>
       </c>
       <c r="BB3" t="n">
-        <v>130100000</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>142900000</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-2200000</v>
+      </c>
       <c r="BD3" t="n">
-        <v>32900000</v>
+        <v>55200000</v>
       </c>
       <c r="BE3" t="n">
-        <v>97200000</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>87700000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
       <c r="BG3" t="n">
-        <v>2460000000</v>
+        <v>2514900000</v>
       </c>
       <c r="BH3" t="n">
-        <v>2460000000</v>
+        <v>2514900000</v>
       </c>
       <c r="BI3" t="n">
-        <v>2328700000</v>
+        <v>2401700000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>131300000</v>
+        <v>113200000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>6612266</v>
+        <v>3896663</v>
       </c>
       <c r="C4" t="n">
-        <v>857976445</v>
+        <v>860692048</v>
       </c>
       <c r="D4" t="n">
         <v>864588711</v>
       </c>
       <c r="E4" t="n">
-        <v>52300000</v>
+        <v>39700000</v>
       </c>
       <c r="F4" t="n">
-        <v>5439900000</v>
+        <v>6274100000</v>
       </c>
       <c r="G4" t="n">
-        <v>5439900000</v>
+        <v>6274100000</v>
       </c>
       <c r="H4" t="n">
-        <v>2451500000</v>
+        <v>2495500000</v>
       </c>
       <c r="I4" t="n">
-        <v>5439900000</v>
+        <v>6274100000</v>
       </c>
       <c r="J4" t="n">
-        <v>52300000</v>
+        <v>39700000</v>
       </c>
       <c r="K4" t="n">
-        <v>5439900000</v>
+        <v>6274100000</v>
       </c>
       <c r="L4" t="n">
-        <v>5439900000</v>
+        <v>6274100000</v>
       </c>
       <c r="M4" t="n">
-        <v>5439900000</v>
+        <v>6274100000</v>
       </c>
       <c r="N4" t="n">
-        <v>5439900000</v>
+        <v>6274100000</v>
       </c>
       <c r="O4" t="n">
-        <v>-733400000</v>
+        <v>86200000</v>
       </c>
       <c r="P4" t="n">
-        <v>6173300000</v>
+        <v>6187900000</v>
       </c>
       <c r="Q4" t="n">
-        <v>6173300000</v>
+        <v>6187900000</v>
       </c>
       <c r="R4" t="n">
-        <v>1638300000</v>
+        <v>1880400000</v>
       </c>
       <c r="S4" t="n">
-        <v>1012800000</v>
+        <v>1161700000</v>
       </c>
       <c r="T4" t="n">
-        <v>10400000</v>
+        <v>10500000</v>
       </c>
       <c r="U4" t="n">
-        <v>10400000</v>
+        <v>10500000</v>
       </c>
       <c r="V4" t="n">
-        <v>451900000</v>
+        <v>560700000</v>
       </c>
       <c r="W4" t="n">
-        <v>451900000</v>
+        <v>560700000</v>
       </c>
       <c r="X4" t="n">
+        <v>28400000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>28400000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>562100000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>718700000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11300000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11300000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>146600000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>560800000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>532300000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>525100000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>8154500000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>4940300000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>39700000</v>
+      </c>
+      <c r="AM4" t="n">
         <v>32800000</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AN4" t="n">
         <v>32800000</v>
       </c>
-      <c r="Z4" t="n">
-        <v>517700000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>625500000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>19500000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>19500000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>143200000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>462800000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>25900000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>436900000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>7800000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>429100000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>7078200000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>4001200000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>40400000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>14500000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>14500000</v>
-      </c>
       <c r="AO4" t="n">
-        <v>862200000</v>
+        <v>958300000</v>
       </c>
       <c r="AP4" t="n">
-        <v>862200000</v>
+        <v>958300000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3084100000</v>
+        <v>3909500000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2083600000</v>
+        <v>-2294900000</v>
       </c>
       <c r="AS4" t="n">
-        <v>5167700000</v>
+        <v>6204400000</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>498000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>3077000000</v>
+        <v>3214200000</v>
       </c>
       <c r="AV4" t="n">
-        <v>10700000</v>
+        <v>11400000</v>
       </c>
       <c r="AW4" t="n">
-        <v>19200000</v>
+        <v>199100000</v>
       </c>
       <c r="AX4" t="n">
-        <v>389300000</v>
+        <v>413600000</v>
       </c>
       <c r="AY4" t="n">
-        <v>64800000</v>
+        <v>82800000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>75100000</v>
+        <v>67900000</v>
       </c>
       <c r="BA4" t="n">
-        <v>249400000</v>
+        <v>262900000</v>
       </c>
       <c r="BB4" t="n">
-        <v>142900000</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-2200000</v>
-      </c>
+        <v>130100000</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>55200000</v>
+        <v>32900000</v>
       </c>
       <c r="BE4" t="n">
-        <v>87700000</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
+        <v>97200000</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>2514900000</v>
+        <v>2460000000</v>
       </c>
       <c r="BH4" t="n">
-        <v>2514900000</v>
+        <v>2460000000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2401700000</v>
+        <v>2328700000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>113200000</v>
+        <v>131300000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>9474920</v>
+        <v>3090081</v>
       </c>
       <c r="C5" t="n">
-        <v>855113791</v>
+        <v>861498630</v>
       </c>
       <c r="D5" t="n">
         <v>864588711</v>
       </c>
       <c r="E5" t="n">
-        <v>54800000</v>
+        <v>29200000</v>
       </c>
       <c r="F5" t="n">
-        <v>4820400000</v>
+        <v>6889400000</v>
       </c>
       <c r="G5" t="n">
-        <v>4820400000</v>
+        <v>6889400000</v>
       </c>
       <c r="H5" t="n">
-        <v>2141200000</v>
+        <v>540100000</v>
       </c>
       <c r="I5" t="n">
-        <v>4820400000</v>
+        <v>6889400000</v>
       </c>
       <c r="J5" t="n">
-        <v>54800000</v>
+        <v>29200000</v>
       </c>
       <c r="K5" t="n">
-        <v>4820400000</v>
+        <v>6889400000</v>
       </c>
       <c r="L5" t="n">
-        <v>4820400000</v>
+        <v>6889400000</v>
       </c>
       <c r="M5" t="n">
-        <v>4820400000</v>
+        <v>6889400000</v>
       </c>
       <c r="N5" t="n">
-        <v>4820400000</v>
+        <v>6889400000</v>
       </c>
       <c r="O5" t="n">
-        <v>-1337500000</v>
+        <v>697200000</v>
       </c>
       <c r="P5" t="n">
-        <v>6157900000</v>
+        <v>6192200000</v>
       </c>
       <c r="Q5" t="n">
-        <v>6157900000</v>
+        <v>6192200000</v>
       </c>
       <c r="R5" t="n">
-        <v>1527600000</v>
+        <v>2561000000</v>
       </c>
       <c r="S5" t="n">
-        <v>996100000</v>
+        <v>1607500000</v>
       </c>
       <c r="T5" t="n">
-        <v>10300000</v>
+        <v>10400000</v>
       </c>
       <c r="U5" t="n">
-        <v>10300000</v>
+        <v>10400000</v>
       </c>
       <c r="V5" t="n">
-        <v>377100000</v>
+        <v>958000000</v>
       </c>
       <c r="W5" t="n">
-        <v>377100000</v>
+        <v>958000000</v>
       </c>
       <c r="X5" t="n">
-        <v>37900000</v>
+        <v>22300000</v>
       </c>
       <c r="Y5" t="n">
-        <v>37900000</v>
+        <v>22300000</v>
       </c>
       <c r="Z5" t="n">
-        <v>570800000</v>
+        <v>616800000</v>
       </c>
       <c r="AA5" t="n">
-        <v>531500000</v>
+        <v>953500000</v>
       </c>
       <c r="AB5" t="n">
-        <v>16900000</v>
+        <v>6900000</v>
       </c>
       <c r="AC5" t="n">
-        <v>16900000</v>
+        <v>6900000</v>
       </c>
       <c r="AD5" t="n">
-        <v>127400000</v>
+        <v>158900000</v>
       </c>
       <c r="AE5" t="n">
-        <v>387200000</v>
+        <v>787700000</v>
       </c>
       <c r="AF5" t="n">
-        <v>25000000</v>
+        <v>36700000</v>
       </c>
       <c r="AG5" t="n">
-        <v>362200000</v>
+        <v>751000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>9300000</v>
+        <v>30400000</v>
       </c>
       <c r="AI5" t="n">
-        <v>352900000</v>
+        <v>720600000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6348000000</v>
+        <v>9450400000</v>
       </c>
       <c r="AK5" t="n">
-        <v>3675300000</v>
+        <v>7956800000</v>
       </c>
       <c r="AL5" t="n">
-        <v>40500000</v>
+        <v>45600000</v>
       </c>
       <c r="AM5" t="n">
-        <v>5800000</v>
+        <v>23400000</v>
       </c>
       <c r="AN5" t="n">
-        <v>5800000</v>
+        <v>23400000</v>
       </c>
       <c r="AO5" t="n">
-        <v>819300000</v>
+        <v>1092900000</v>
       </c>
       <c r="AP5" t="n">
-        <v>819300000</v>
+        <v>1092900000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2809700000</v>
+        <v>6794900000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-2059100000</v>
+        <v>-2494500000</v>
       </c>
       <c r="AS5" t="n">
-        <v>4868800000</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
+        <v>9289400000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3219600000</v>
+      </c>
       <c r="AU5" t="n">
-        <v>2672700000</v>
+        <v>1493600000</v>
       </c>
       <c r="AV5" t="n">
-        <v>10300000</v>
+        <v>12300000</v>
       </c>
       <c r="AW5" t="n">
-        <v>17400000</v>
+        <v>159100000</v>
       </c>
       <c r="AX5" t="n">
-        <v>340000000</v>
+        <v>460000000</v>
       </c>
       <c r="AY5" t="n">
-        <v>49900000</v>
+        <v>105600000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>59600000</v>
+        <v>79900000</v>
       </c>
       <c r="BA5" t="n">
-        <v>230500000</v>
+        <v>274500000</v>
       </c>
       <c r="BB5" t="n">
-        <v>135300000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>-1200000</v>
-      </c>
+        <v>353000000</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>20000000</v>
+        <v>44500000</v>
       </c>
       <c r="BE5" t="n">
-        <v>58800000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>56500000</v>
-      </c>
+        <v>306400000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>2169700000</v>
+        <v>509200000</v>
       </c>
       <c r="BH5" t="n">
-        <v>2169700000</v>
+        <v>509200000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2069200000</v>
+        <v>392400000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>100500000</v>
+        <v>116800000</v>
       </c>
     </row>
   </sheetData>
@@ -2634,622 +2634,622 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-1140500000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>1177700000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
       <c r="D2" t="n">
-        <v>-19000000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>-11600000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
       <c r="G2" t="n">
-        <v>-2985700000</v>
+        <v>-395700000</v>
       </c>
       <c r="H2" t="n">
-        <v>521500000</v>
+        <v>2180000000</v>
       </c>
       <c r="I2" t="n">
-        <v>2471400000</v>
+        <v>1715100000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1800000</v>
+        <v>-8400000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1948100000</v>
+        <v>473300000</v>
       </c>
       <c r="L2" t="n">
-        <v>-750700000</v>
+        <v>-653500000</v>
       </c>
       <c r="M2" t="n">
-        <v>-750700000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>-653500000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-1000000</v>
+      </c>
       <c r="O2" t="n">
-        <v>-731700000</v>
+        <v>-640900000</v>
       </c>
       <c r="P2" t="n">
-        <v>-731700000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>-640900000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
       <c r="T2" t="n">
-        <v>-19000000</v>
+        <v>-11600000</v>
       </c>
       <c r="U2" t="n">
-        <v>-19000000</v>
+        <v>-11600000</v>
       </c>
       <c r="V2" t="n">
-        <v>-19000000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>-11600000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
-        <v>-3042600000</v>
+        <v>-446600000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3042600000</v>
+        <v>-446600000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-23400000</v>
+        <v>-51000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-33800000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-33800000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2985400000</v>
+        <v>-395600000</v>
       </c>
       <c r="AD2" t="n">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2985700000</v>
+        <v>-395700000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1845200000</v>
+        <v>1573400000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1845200000</v>
+        <v>1573400000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-72500000</v>
+        <v>-452100000</v>
       </c>
       <c r="AI2" t="n">
-        <v>154600000</v>
+        <v>105900000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-4500000</v>
+        <v>-7500000</v>
       </c>
       <c r="AK2" t="n">
-        <v>29300000</v>
+        <v>76100000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-111000000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>-186800000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-8100000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>198100000</v>
+        <v>-149000000</v>
       </c>
       <c r="AO2" t="n">
-        <v>198100000</v>
+        <v>-149000000</v>
       </c>
       <c r="AP2" t="n">
-        <v>198100000</v>
+        <v>-149000000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-12900000</v>
+        <v>-44700000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-296200000</v>
+        <v>6900000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-296200000</v>
+        <v>6900000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-263800000</v>
+        <v>-149900000</v>
       </c>
       <c r="AU2" t="n">
-        <v>26400000</v>
+        <v>-28300000</v>
       </c>
       <c r="AV2" t="n">
-        <v>488200000</v>
+        <v>523700000</v>
       </c>
       <c r="AW2" t="n">
-        <v>488200000</v>
+        <v>523700000</v>
       </c>
       <c r="AX2" t="n">
-        <v>270400000</v>
+        <v>252500000</v>
       </c>
       <c r="AY2" t="n">
-        <v>270400000</v>
+        <v>252500000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>270400000</v>
+        <v>252500000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-600000</v>
+        <v>-100000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-600000</v>
+        <v>-100000</v>
       </c>
       <c r="BC2" t="n">
-        <v>1328700000</v>
+        <v>1439900000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>510400000</v>
+        <v>913700000</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>-16900000</v>
+        <v>-19700000</v>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" t="n">
-        <v>-1145200000</v>
+        <v>-584100000</v>
       </c>
       <c r="H3" t="n">
-        <v>2471400000</v>
+        <v>2525600000</v>
       </c>
       <c r="I3" t="n">
-        <v>2525600000</v>
+        <v>2180000000</v>
       </c>
       <c r="J3" t="n">
-        <v>8900000</v>
+        <v>7000000</v>
       </c>
       <c r="K3" t="n">
-        <v>-63100000</v>
+        <v>338600000</v>
       </c>
       <c r="L3" t="n">
-        <v>-532200000</v>
+        <v>-533000000</v>
       </c>
       <c r="M3" t="n">
-        <v>-532200000</v>
+        <v>-533000000</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-515300000</v>
+        <v>-513300000</v>
       </c>
       <c r="P3" t="n">
-        <v>-515300000</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>-513300000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
       <c r="T3" t="n">
-        <v>-16900000</v>
+        <v>-19700000</v>
       </c>
       <c r="U3" t="n">
-        <v>-16900000</v>
+        <v>-19700000</v>
       </c>
       <c r="V3" t="n">
-        <v>-16900000</v>
+        <v>-19700000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-1186500000</v>
+        <v>-626200000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1186500000</v>
+        <v>-626200000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-13800000</v>
+        <v>-25400000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-28400000</v>
+        <v>-28900000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-28400000</v>
+        <v>-28900000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1144300000</v>
+        <v>-571900000</v>
       </c>
       <c r="AD3" t="n">
-        <v>900000</v>
+        <v>12200000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1145200000</v>
+        <v>-584100000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1655600000</v>
+        <v>1497800000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1655600000</v>
+        <v>1497800000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-314800000</v>
+        <v>-262700000</v>
       </c>
       <c r="AI3" t="n">
-        <v>188600000</v>
+        <v>111100000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-5200000</v>
+        <v>-7700000</v>
       </c>
       <c r="AK3" t="n">
-        <v>78300000</v>
+        <v>71500000</v>
       </c>
       <c r="AL3" t="n">
-        <v>56800000</v>
+        <v>78100000</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>50500000</v>
+        <v>71300000</v>
       </c>
       <c r="AO3" t="n">
-        <v>50500000</v>
+        <v>71300000</v>
       </c>
       <c r="AP3" t="n">
-        <v>50500000</v>
+        <v>71300000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-13600000</v>
+        <v>-18900000</v>
       </c>
       <c r="AR3" t="n">
-        <v>19900000</v>
+        <v>25700000</v>
       </c>
       <c r="AS3" t="n">
-        <v>19900000</v>
+        <v>25700000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-263700000</v>
+        <v>-230000000</v>
       </c>
       <c r="AU3" t="n">
-        <v>22000000</v>
+        <v>18400000</v>
       </c>
       <c r="AV3" t="n">
-        <v>405000000</v>
+        <v>334300000</v>
       </c>
       <c r="AW3" t="n">
-        <v>405000000</v>
+        <v>334300000</v>
       </c>
       <c r="AX3" t="n">
-        <v>217500000</v>
+        <v>267600000</v>
       </c>
       <c r="AY3" t="n">
-        <v>217500000</v>
+        <v>267600000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>217500000</v>
+        <v>267600000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-10300000</v>
+        <v>-6600000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-10300000</v>
+        <v>-6600000</v>
       </c>
       <c r="BC3" t="n">
-        <v>1281400000</v>
+        <v>1123800000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>913700000</v>
+        <v>510400000</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-19700000</v>
+        <v>-16900000</v>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>-584100000</v>
+        <v>-1145200000</v>
       </c>
       <c r="H4" t="n">
+        <v>2471400000</v>
+      </c>
+      <c r="I4" t="n">
         <v>2525600000</v>
       </c>
-      <c r="I4" t="n">
-        <v>2180000000</v>
-      </c>
       <c r="J4" t="n">
-        <v>7000000</v>
+        <v>8900000</v>
       </c>
       <c r="K4" t="n">
-        <v>338600000</v>
+        <v>-63100000</v>
       </c>
       <c r="L4" t="n">
-        <v>-533000000</v>
+        <v>-532200000</v>
       </c>
       <c r="M4" t="n">
-        <v>-533000000</v>
+        <v>-532200000</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-513300000</v>
+        <v>-515300000</v>
       </c>
       <c r="P4" t="n">
-        <v>-513300000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
+        <v>-515300000</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>-19700000</v>
+        <v>-16900000</v>
       </c>
       <c r="U4" t="n">
-        <v>-19700000</v>
+        <v>-16900000</v>
       </c>
       <c r="V4" t="n">
-        <v>-19700000</v>
+        <v>-16900000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-626200000</v>
+        <v>-1186500000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-626200000</v>
+        <v>-1186500000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-25400000</v>
+        <v>-13800000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-28900000</v>
+        <v>-28400000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-28900000</v>
+        <v>-28400000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-571900000</v>
+        <v>-1144300000</v>
       </c>
       <c r="AD4" t="n">
-        <v>12200000</v>
+        <v>900000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-584100000</v>
+        <v>-1145200000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1497800000</v>
+        <v>1655600000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1497800000</v>
+        <v>1655600000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-262700000</v>
+        <v>-314800000</v>
       </c>
       <c r="AI4" t="n">
-        <v>111100000</v>
+        <v>188600000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-7700000</v>
+        <v>-5200000</v>
       </c>
       <c r="AK4" t="n">
-        <v>71500000</v>
+        <v>78300000</v>
       </c>
       <c r="AL4" t="n">
-        <v>78100000</v>
+        <v>56800000</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>71300000</v>
+        <v>50500000</v>
       </c>
       <c r="AO4" t="n">
-        <v>71300000</v>
+        <v>50500000</v>
       </c>
       <c r="AP4" t="n">
-        <v>71300000</v>
+        <v>50500000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-18900000</v>
+        <v>-13600000</v>
       </c>
       <c r="AR4" t="n">
-        <v>25700000</v>
+        <v>19900000</v>
       </c>
       <c r="AS4" t="n">
-        <v>25700000</v>
+        <v>19900000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-230000000</v>
+        <v>-263700000</v>
       </c>
       <c r="AU4" t="n">
-        <v>18400000</v>
+        <v>22000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>334300000</v>
+        <v>405000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>334300000</v>
+        <v>405000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>267600000</v>
+        <v>217500000</v>
       </c>
       <c r="AY4" t="n">
-        <v>267600000</v>
+        <v>217500000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>267600000</v>
+        <v>217500000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-6600000</v>
+        <v>-10300000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-6600000</v>
+        <v>-10300000</v>
       </c>
       <c r="BC4" t="n">
-        <v>1123800000</v>
+        <v>1281400000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>1177700000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
+        <v>-1140500000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-11600000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+        <v>-19000000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-395700000</v>
+        <v>-2985700000</v>
       </c>
       <c r="H5" t="n">
-        <v>2180000000</v>
+        <v>521500000</v>
       </c>
       <c r="I5" t="n">
-        <v>1715100000</v>
+        <v>2471400000</v>
       </c>
       <c r="J5" t="n">
-        <v>-8400000</v>
+        <v>-1800000</v>
       </c>
       <c r="K5" t="n">
-        <v>473300000</v>
+        <v>-1948100000</v>
       </c>
       <c r="L5" t="n">
-        <v>-653500000</v>
+        <v>-750700000</v>
       </c>
       <c r="M5" t="n">
-        <v>-653500000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1000000</v>
-      </c>
+        <v>-750700000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>-640900000</v>
+        <v>-731700000</v>
       </c>
       <c r="P5" t="n">
-        <v>-640900000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
+        <v>-731700000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-11600000</v>
+        <v>-19000000</v>
       </c>
       <c r="U5" t="n">
-        <v>-11600000</v>
+        <v>-19000000</v>
       </c>
       <c r="V5" t="n">
-        <v>-11600000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
+        <v>-19000000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-446600000</v>
+        <v>-3042600000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-446600000</v>
+        <v>-3042600000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-51000000</v>
+        <v>-23400000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-33800000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-33800000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-395600000</v>
+        <v>-2985400000</v>
       </c>
       <c r="AD5" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-395700000</v>
+        <v>-2985700000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1573400000</v>
+        <v>1845200000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1573400000</v>
+        <v>1845200000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-452100000</v>
+        <v>-72500000</v>
       </c>
       <c r="AI5" t="n">
-        <v>105900000</v>
+        <v>154600000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-7500000</v>
+        <v>-4500000</v>
       </c>
       <c r="AK5" t="n">
-        <v>76100000</v>
+        <v>29300000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-186800000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-8100000</v>
-      </c>
+        <v>-111000000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>-149000000</v>
+        <v>198100000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-149000000</v>
+        <v>198100000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-149000000</v>
+        <v>198100000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-44700000</v>
+        <v>-12900000</v>
       </c>
       <c r="AR5" t="n">
-        <v>6900000</v>
+        <v>-296200000</v>
       </c>
       <c r="AS5" t="n">
-        <v>6900000</v>
+        <v>-296200000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-149900000</v>
+        <v>-263800000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-28300000</v>
+        <v>26400000</v>
       </c>
       <c r="AV5" t="n">
-        <v>523700000</v>
+        <v>488200000</v>
       </c>
       <c r="AW5" t="n">
-        <v>523700000</v>
+        <v>488200000</v>
       </c>
       <c r="AX5" t="n">
-        <v>252500000</v>
+        <v>270400000</v>
       </c>
       <c r="AY5" t="n">
-        <v>252500000</v>
+        <v>270400000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>252500000</v>
+        <v>270400000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-100000</v>
+        <v>-600000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-100000</v>
+        <v>-600000</v>
       </c>
       <c r="BC5" t="n">
-        <v>1439900000</v>
+        <v>1328700000</v>
       </c>
     </row>
   </sheetData>
@@ -3739,192 +3739,192 @@
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EC1" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Daniel Johannes Pretorius B.Proc., L.L.M., LLB', 'age': 58, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1967, 'fiscalYear': 2025, 'totalPay': 1152334, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wilhelm Jacobus Schoeman BTech Ana', 'age': 51, 'title': 'Chief Operating Officer', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 675531, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Henriette  Hooijer B.Com., C.A.', 'age': 44, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1981, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shalin  Naidoo B.Tech., M.B.A.', 'age': 48, 'title': 'Chief Information &amp; Technology Officer', 'yearBorn': 1977, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Refiloe  Vengeni B.Com., L.L.B.', 'age': 36, 'title': 'Legal Counsel', 'yearBorn': 1989, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kevin Peter Kruger M.D., P., P.M.B.', 'age': 57, 'title': 'Head of Technical Services', 'yearBorn': 1968, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Henry  Gouws MDP', 'age': 56, 'title': 'Head of Operations', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kgomotso  Mbanyele', 'age': 44, 'title': 'Company Secretary', 'yearBorn': 1981, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Daniel Johannes Pretorius B.Proc., L.L.M., LLB', 'age': 58, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1967, 'fiscalYear': 2025, 'totalPay': 1137402, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wilhelm Jacobus Schoeman BTech Ana', 'age': 51, 'title': 'Chief Operating Officer', 'yearBorn': 1974, 'fiscalYear': 2025, 'totalPay': 666778, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Henriette  Hooijer B.Com., C.A.', 'age': 44, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1981, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shalin  Naidoo B.Tech., M.B.A.', 'age': 48, 'title': 'Chief Information &amp; Technology Officer', 'yearBorn': 1977, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Refiloe  Vengeni B.Com., L.L.B.', 'age': 36, 'title': 'Legal Counsel', 'yearBorn': 1989, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kevin Peter Kruger M.D., P., P.M.B.', 'age': 57, 'title': 'Head of Technical Services', 'yearBorn': 1968, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Henry  Gouws MDP', 'age': 56, 'title': 'Head of Operations', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kgomotso  Mbanyele', 'age': 44, 'title': 'Company Secretary', 'yearBorn': 1981, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4006,37 +4006,37 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>25.6</v>
+        <v>23.96</v>
       </c>
       <c r="U2" t="n">
-        <v>26.57</v>
+        <v>22.93</v>
       </c>
       <c r="V2" t="n">
-        <v>25.62</v>
+        <v>22.33</v>
       </c>
       <c r="W2" t="n">
-        <v>26.66</v>
+        <v>22.9805</v>
       </c>
       <c r="X2" t="n">
-        <v>25.6</v>
+        <v>23.96</v>
       </c>
       <c r="Y2" t="n">
-        <v>26.57</v>
+        <v>22.93</v>
       </c>
       <c r="Z2" t="n">
-        <v>25.62</v>
+        <v>22.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>26.66</v>
+        <v>22.9805</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.427</v>
+        <v>0.43</v>
       </c>
       <c r="AC2" t="n">
-        <v>796</v>
+        <v>591</v>
       </c>
       <c r="AD2" t="n">
-        <v>796</v>
+        <v>591</v>
       </c>
       <c r="AE2" t="n">
         <v>1793</v>
@@ -4054,13 +4054,13 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2218326569</v>
+        <v>1918054484</v>
       </c>
       <c r="AK2" t="n">
         <v>6.53</v>
       </c>
       <c r="AL2" t="n">
-        <v>26.66</v>
+        <v>22.9805</v>
       </c>
       <c r="AM2" t="n">
         <v>17.64983</v>
@@ -4078,7 +4078,7 @@
         <v>9</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.3515625</v>
+        <v>0.37562606</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -4089,25 +4089,25 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>20718979072</v>
+        <v>255331968</v>
       </c>
       <c r="AV2" t="n">
         <v>0.35056</v>
       </c>
       <c r="AW2" t="n">
-        <v>431617096</v>
+        <v>43161710</v>
       </c>
       <c r="AX2" t="n">
         <v>0.00025</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.12552</v>
+        <v>0.12544</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.630251</v>
+        <v>7.559664</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.378657</v>
+        <v>3.0384948</v>
       </c>
       <c r="BB2" t="n">
         <v>1751241600</v>
@@ -4125,16 +4125,16 @@
         <v>3200300032</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.27</v>
+        <v>0.028</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.611</v>
+        <v>0.057</v>
       </c>
       <c r="BI2" t="n">
         <v>-0.3154856</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BK2" t="n">
         <v>0.295536</v>
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="BN2" t="n">
-        <v>25.78</v>
+        <v>22.97</v>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>1734400000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2</v>
+        <v>19.995</v>
       </c>
       <c r="BR2" t="n">
         <v>4493400064</v>
@@ -4250,143 +4250,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>0.7031262</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>25.78</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>LSE</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>finmb_527041</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>DRDGOLD LTD DRDGOLD ADR REPRESE</t>
+          <t>Europe/London</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>BST</t>
         </is>
       </c>
       <c r="CU2" t="n">
-        <v>1780423645</v>
+        <v>3600000</v>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>LSE</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>finmb_527041</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>Europe/London</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>BST</t>
-        </is>
+          <t>gb_market</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
+        <v>14.7885275</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1.8075632</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>14.522039</v>
       </c>
       <c r="CZ2" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>gb_market</t>
-        </is>
-      </c>
-      <c r="DB2" t="b">
-        <v>0</v>
+        <v>1.7189996</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>15</v>
       </c>
       <c r="DC2" t="b">
         <v>0</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>1782151629</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-4.1318855</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>DRDGOLD LTD DRDGOLD ADR REPRESE</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>DRDGOLD Limited</t>
+        </is>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
         <v>1222844400000</v>
       </c>
-      <c r="DE2" t="n">
-        <v>0.1800003</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>25.62 - 26.66</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DL2" t="n">
+        <v>-0.9899998</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>22.33 - 22.9805</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
         <is>
           <t>LSE</t>
         </is>
       </c>
-      <c r="DH2" t="n">
+      <c r="DO2" t="n">
         <v>1793</v>
       </c>
-      <c r="DI2" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>2.9479325</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>6.53 - 26.66</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.87999916</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.03300822</v>
-      </c>
-      <c r="DN2" t="n">
+      <c r="DP2" t="n">
+        <v>16.439999</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>2.5176108</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>6.53 - 22.9805</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.010499954</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.00045690715</v>
+      </c>
+      <c r="DU2" t="n">
         <v>-31.54856</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="DV2" t="n">
         <v>1771432200</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DW2" t="n">
         <v>1771432200</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DX2" t="n">
         <v>1771401600</v>
       </c>
-      <c r="DR2" t="n">
+      <c r="DY2" t="n">
         <v>1771401600</v>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>17.59853</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>2.1510224</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>17.33204</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>2.0516243</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>15</v>
       </c>
       <c r="DZ2" t="b">
         <v>0</v>
       </c>
       <c r="EA2" t="inlineStr">
         <is>
-          <t>POSTPOST</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>DRDGOLD Limited</t>
-        </is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EB2" t="b">
+        <v>0</v>
       </c>
       <c r="EC2" t="inlineStr"/>
     </row>
